--- a/data/trans_orig/IP07A02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A02-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 99,4%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46711</t>
+          <t>46965</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64497</t>
+          <t>64068</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63884</t>
+          <t>64400</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82893</t>
+          <t>83210</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116391</t>
+          <t>116689</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142360</t>
+          <t>143001</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50726</t>
+          <t>50751</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68505</t>
+          <t>67633</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50816</t>
+          <t>50916</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69377</t>
+          <t>69441</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105918</t>
+          <t>107000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133062</t>
+          <t>132671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16045</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>9835</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22301</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92767</t>
+          <t>93286</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114889</t>
+          <t>115678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103880</t>
+          <t>104091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125943</t>
+          <t>126053</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>204678</t>
+          <t>203624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235356</t>
+          <t>236191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,43%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67613</t>
+          <t>67740</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89178</t>
+          <t>89232</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63815</t>
+          <t>64584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86356</t>
+          <t>85930</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136438</t>
+          <t>137054</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>167402</t>
+          <t>168020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27769</t>
+          <t>27097</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145782</t>
+          <t>145351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>174280</t>
+          <t>175179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>174714</t>
+          <t>172278</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203520</t>
+          <t>204023</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>328176</t>
+          <t>327218</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>369103</t>
+          <t>369716</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,58%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122861</t>
+          <t>122966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151491</t>
+          <t>152239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121441</t>
+          <t>120362</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>150070</t>
+          <t>149107</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254883</t>
+          <t>250931</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>295138</t>
+          <t>290826</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>26987</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25661</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44356</t>
+          <t>44750</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56831</t>
+          <t>56873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77007</t>
+          <t>77940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63017</t>
+          <t>63401</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83769</t>
+          <t>83466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125908</t>
+          <t>127736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154666</t>
+          <t>155804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63993</t>
+          <t>64261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84503</t>
+          <t>85078</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61345</t>
+          <t>62408</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82407</t>
+          <t>81096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132557</t>
+          <t>131145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162565</t>
+          <t>159932</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13516</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>28187</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -3347,62 +3347,62 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5392</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4937</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4721</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1331</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4554</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45979</t>
+          <t>46746</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65951</t>
+          <t>66996</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67199</t>
+          <t>67875</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88368</t>
+          <t>89649</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119840</t>
+          <t>118583</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149844</t>
+          <t>148247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,35%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87012</t>
+          <t>85623</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108539</t>
+          <t>107167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69212</t>
+          <t>68079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90890</t>
+          <t>89619</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160145</t>
+          <t>160511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>191063</t>
+          <t>190070</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,57%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19260</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7770</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18562</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35071</t>
+          <t>34738</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>597</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108097</t>
+          <t>108446</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136563</t>
+          <t>136731</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135625</t>
+          <t>137516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>165157</t>
+          <t>166651</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255180</t>
+          <t>253635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>296780</t>
+          <t>294191</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157650</t>
+          <t>157122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187118</t>
+          <t>185586</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136557</t>
+          <t>133764</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166568</t>
+          <t>164726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>298700</t>
+          <t>301737</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>343914</t>
+          <t>342502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>17269</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>28670</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>35169</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>57174</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97117</t>
+          <t>96288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118226</t>
+          <t>119271</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114606</t>
+          <t>115517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136366</t>
+          <t>139028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218109</t>
+          <t>217760</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248059</t>
+          <t>249198</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,88%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57200</t>
+          <t>56662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77804</t>
+          <t>79616</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42217</t>
+          <t>39545</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62903</t>
+          <t>62066</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106557</t>
+          <t>105032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136110</t>
+          <t>135333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78234</t>
+          <t>79580</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99868</t>
+          <t>101072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99640</t>
+          <t>99861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121530</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186272</t>
+          <t>185239</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217574</t>
+          <t>217245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57682</t>
+          <t>57098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79442</t>
+          <t>78373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42288</t>
+          <t>42446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62950</t>
+          <t>63045</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104528</t>
+          <t>105083</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135428</t>
+          <t>136746</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10334</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>23978</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>715</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181633</t>
+          <t>183699</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>213641</t>
+          <t>212931</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>222138</t>
+          <t>219998</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>251939</t>
+          <t>252274</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>413795</t>
+          <t>414250</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>458273</t>
+          <t>457316</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118909</t>
+          <t>120662</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149764</t>
+          <t>149727</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119371</t>
+          <t>119827</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215620</t>
+          <t>217282</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259512</t>
+          <t>260519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11508</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>19729</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>21542</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39967</t>
+          <t>40805</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14769</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>718</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A02-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2007 (tasa de respuesta: 99,4%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>73670</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63898</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>82143</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>58,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>55392</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>46965</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>64068</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>46539</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>63890</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>43,9%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>73670</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>64400</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>83210</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,06%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116689</t>
+          <t>115713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143001</t>
+          <t>142529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -840,67 +840,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>60018</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51325</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>69650</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>36,27%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>59444</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50751</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67633</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50535</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67897</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>47,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>53,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60018</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>50916</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>69441</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>42,41%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107000</t>
+          <t>105823</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132671</t>
+          <t>133107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4724</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9872</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>10178</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5984</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16463</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6026</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>16306</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>8,07%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4724</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2056</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9835</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21619</t>
+          <t>21605</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1810</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5021</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1159</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4173</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3784</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4713</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4552</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1293</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4601</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4490</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4461</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>126172</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>126172</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>126172</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>114858</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>103341</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>125524</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>61,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>104064</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>93286</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>115678</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>93336</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>115161</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>53,61%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>114858</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>104091</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>126053</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203624</t>
+          <t>202814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236191</t>
+          <t>234194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74496</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>63909</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86024</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,43%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>78342</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67740</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>89232</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>67475</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>89600</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,36%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74496</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>64584</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>85930</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,63%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>137054</t>
+          <t>138624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168020</t>
+          <t>168141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10730</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6534</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17013</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>9024</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5016</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14829</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4998</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>15247</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,65%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10730</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6048</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>17313</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27097</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -1743,107 +1743,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3570</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2666</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6678</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3249</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>7295</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3310</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7374</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1856,92 +1856,92 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2625</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6523</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>2625</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6527</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>203353</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>203353</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>203353</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>203353</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>203353</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>203353</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>188528</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>174416</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>205363</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>54,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>50,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>59,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>159456</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>145351</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>175179</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>146045</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>173707</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>49,79%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>54,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>188528</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>172278</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>204023</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>54,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>327218</t>
+          <t>326752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>369716</t>
+          <t>369886</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>134513</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>119711</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>150510</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,71%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>137786</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>122966</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>152239</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>123098</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>151519</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>43,02%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>38,39%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>47,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>134513</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>120362</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>149107</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>39,0%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>250931</t>
+          <t>250495</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>290826</t>
+          <t>293131</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15454</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10120</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>22351</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>19202</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>12995</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26987</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13246</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>27247</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>15454</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>9972</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>22478</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26175</t>
+          <t>26593</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44750</t>
+          <t>45313</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5417</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3825</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1325</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8359</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1743</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7932</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6247</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -2538,92 +2538,92 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3919</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8342</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>3919</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7934</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>3919</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>344868</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>344868</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>344868</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>320269</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>320269</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>320269</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>344868</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>344868</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>344868</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>73358</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63259</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>84193</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>53,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>67167</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>56873</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>77940</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>55978</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>76731</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>43,38%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>73358</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>63401</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>83466</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>47,05%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127736</t>
+          <t>126418</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155804</t>
+          <t>155033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,89%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>71835</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61235</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>82257</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39,27%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,75%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>74356</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>64261</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>85078</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>64657</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>85895</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>48,02%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>54,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>71835</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>62408</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>81096</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>46,07%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131145</t>
+          <t>130883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159932</t>
+          <t>159635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8119</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14937</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11513</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6768</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17698</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6952</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>18244</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,44%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8119</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>4248</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>13233</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28187</t>
+          <t>28814</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4674</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1803</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5392</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5062</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1331</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4721</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3450,107 +3450,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4493</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1287</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3941</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3885</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155930</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155930</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155930</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>155930</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>155930</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>155930</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>78071</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>67512</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>87546</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>44,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>50,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>55984</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46746</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>66996</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>46208</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>65970</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,5%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>78071</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>67875</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>89649</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>44,64%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118583</t>
+          <t>118368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>148247</t>
+          <t>148494</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>78809</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69594</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>89497</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,18%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>96966</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>85623</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>107167</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>86059</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>107100</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>58,02%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>51,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>64,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>78809</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>68079</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>89619</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>45,06%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160511</t>
+          <t>160500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190070</t>
+          <t>190052</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12576</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7788</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18544</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>12705</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7731</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19409</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7711</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>19767</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,6%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12576</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7568</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19127</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17941</t>
+          <t>18477</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34738</t>
+          <t>33488</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7575</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4118</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4291</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1277</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8230</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2952</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5163</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174883</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174883</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174883</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174883</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174883</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174883</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>151429</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>136168</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>166389</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>41,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>50,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>123151</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>108446</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>136731</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>108542</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>137750</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>38,25%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>33,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>42,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>151429</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>137516</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>166651</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>45,77%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>253635</t>
+          <t>255176</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>294191</t>
+          <t>295842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>150644</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136982</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>165957</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,54%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>41,41%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>171322</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>157122</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>185586</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>157429</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>186879</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>53,21%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>48,8%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>57,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>150644</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>133764</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>164726</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>45,54%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>301737</t>
+          <t>301404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342502</t>
+          <t>342360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20695</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14042</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>28781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>24218</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17269</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>33272</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>17300</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>33506</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,52%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>20695</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>13966</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>28670</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35169</t>
+          <t>35832</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57174</t>
+          <t>56883</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -4701,107 +4701,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4812</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9492</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6103</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6598</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4812</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>9968</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>7433</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>12870</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>7433</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>3858</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>12954</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6579</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3295</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3537</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3234</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7574</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>330813</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>330813</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>330813</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321969</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321969</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321969</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>330813</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>330813</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>330813</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>126117</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>116134</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>137120</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>62,22%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>73,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>107822</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>96288</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>119271</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>97001</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>118065</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,97%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,77%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>126117</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>115517</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>139028</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>67,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>217760</t>
+          <t>219353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249198</t>
+          <t>248789</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51704</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>40924</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61547</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,7%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32,98%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>67648</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56662</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>79616</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>57893</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>78752</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,47%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51704</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>39545</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62066</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>27,7%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105032</t>
+          <t>105751</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135333</t>
+          <t>134786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7347</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4046</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13173</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,06%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6338</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3310</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12028</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3007</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11583</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,41%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7347</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3776</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>13357</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>21108</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5578</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2766</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7058</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5115</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -5726,107 +5726,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1409</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5142</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4420</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1409</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5159</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1409</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4834</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>186641</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>186641</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>186641</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>186641</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>186641</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>186641</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>111080</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100918</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>121260</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>64,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>69,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>89901</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>79580</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101072</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>78259</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>100535</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>52,85%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>111080</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>99861</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>121200</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>64,05%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185239</t>
+          <t>185962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217245</t>
+          <t>216299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>52331</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>42114</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>63056</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>30,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,28%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>36,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67512</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57098</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>78373</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>56512</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>78866</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,69%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>52331</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>42446</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>63045</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>30,17%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105083</t>
+          <t>105138</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136746</t>
+          <t>133621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5354</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10041</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11049</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6481</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17410</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6544</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18019</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,5%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5354</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2563</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10639</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2373</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7117</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1640</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6229</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5869</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2373</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6406</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -6408,92 +6408,92 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6304</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>2300</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6170</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173437</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173437</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173437</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170102</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170102</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170102</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173437</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173437</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173437</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>237197</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>222465</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>252297</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>65,87%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>197723</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>183699</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>212931</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>181514</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>213082</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>55,53%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>51,59%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>59,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>237197</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>219998</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>252274</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>65,87%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>414250</t>
+          <t>413343</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>457316</t>
+          <t>458403</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>104035</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>90699</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>119425</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>28,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>33,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>135159</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>120662</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>149727</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>119613</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>150489</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,96%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>42,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>104035</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>89940</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>119827</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>28,89%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217282</t>
+          <t>217243</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>260519</t>
+          <t>260373</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12702</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7942</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>19815</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>17388</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>11161</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>25907</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>11755</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>26581</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,88%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>12702</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>8027</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>19729</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21542</t>
+          <t>22531</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40805</t>
+          <t>41765</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -6977,67 +6977,67 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3845</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8570</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>4406</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1824</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9056</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1835</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8977</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3845</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1478</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>9056</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14769</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -7090,107 +7090,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6451</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1409</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4978</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4921</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6205</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>3709</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>8607</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>3709</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>8071</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>360078</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>360078</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>360078</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>356085</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>356085</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>356085</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>360078</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>360078</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>360078</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
